--- a/Horas Asignaturas.xlsx
+++ b/Horas Asignaturas.xlsx
@@ -45,7 +45,7 @@
     <t>Ingles</t>
   </si>
   <si>
-    <t>IP I</t>
+    <t>Digitalización</t>
   </si>
 </sst>
 </file>
